--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>19/07 21:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>18/07 17:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>19/07 21:45</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>55</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>19/07 19:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>20/07 19:45</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>21/07 00:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>50</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>20/07 09:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>45</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>21/07 18:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>15/07 18:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>45</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>17/07 01:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>15/07 08:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F15" t="n">
+        <v>4.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>18/07 23:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>15/07 04:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F17" t="n">
+        <v>2.7</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>15/07 19:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>28.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>28</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>15/07 02:10</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>17/07 17:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>40</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>15/07 09:40</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F21" t="n">
+        <v>2.15</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>19/07 01:10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>19/07 00:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>16/07 11:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F24" t="n">
+        <v>2.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>17/07 16:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>40</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>15/07 09:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F26" t="n">
+        <v>3.4</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45853.08294051729</v>
+        <v>45853.08294052084</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1X | Viktoria P</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Viktoria Plzen – Servette FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+0,66%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45853.15452352616</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F27" t="n">
+        <v>1.2</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,97 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45853.15452352616</v>
+        <v>45853.15452353009</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Osters IF </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Osters IF – Malmo FFAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>19/07 13:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+2,31%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45853.1951951137</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Petrolu</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FC Petrolul Ploiesti – FCSBLiga 1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19/07 18:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+0,95%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45853.1951951137</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>19/07 13:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>50</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45853.1951951137</v>
+        <v>45853.19519511574</v>
       </c>
     </row>
     <row r="29">
@@ -1668,23 +1666,111 @@
           <t>19/07 18:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>40</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+0,95%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45853.19519511574</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Defensa y </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia – CA AldosiviLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>22/07 00:15</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>+0,95%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>45853.1951951137</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+3,76%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45853.22731032178</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Tigre –</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CA Tigre – Argentinos JuniorsLiga Profesional stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20/07 13:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+3,40%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45853.22731032178</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>40</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45853.22731032178</v>
+        <v>45853.22731032407</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>20/07 13:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>40</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,187 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45853.22731032178</v>
+        <v>45853.22731032407</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Nashville </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Nashville SC – Toronto FCMLS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20/07 00:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+12,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45853.27471697073</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Bahia Salv</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bahia Salvador BA – America de CaliInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>16/07 00:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+7,65%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45853.27471697073</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | New York R</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York Red Bulls – New England RevolutionÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>16/07 23:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+6,52%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45853.27471697073</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | Houston Dy</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Houston Dynamo – Vancouver WhitecapsÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>27,9%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+3,09%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45853.27471697073</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>20/07 00:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>50</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45853.27471697073</v>
+        <v>45853.27471696759</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2.7</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45853.27471697073</v>
+        <v>45853.27471696759</v>
       </c>
     </row>
     <row r="34">
@@ -1885,10 +1881,8 @@
           <t>16/07 23:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1901,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45853.27471697073</v>
+        <v>45853.27471696759</v>
       </c>
     </row>
     <row r="35">
@@ -1930,10 +1924,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="F35" t="n">
+        <v>3.7</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1946,7 +1938,52 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45853.27471697073</v>
+        <v>45853.27471696759</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Juan Manue</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Juan Manuel Cerundolo – Jan-Lennard StruffATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>15/07 08:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45853.30881782836</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -1967,10 +1967,8 @@
           <t>15/07 08:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F36" t="n">
+        <v>3.5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45853.30881782836</v>
+        <v>45853.30881782407</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,141 @@
         <v>45853.30881782407</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Bahia Salv</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bahia Salvador BA – America de CaliInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16/07 00:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>39,1%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+13,4%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45853.39681537616</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs1re équipe | Central Có</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Central Córdoba – Cerro Largo FCInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>15/07 22:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>33,9%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+8,46%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45853.39681537616</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Univers</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>FC Universitatea Cluj – UTA AradLiga 1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19/07 15:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+4,86%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45853.39681537616</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45853.39681537616</v>
+        <v>45853.39681538194</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>15/07 22:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F38" t="n">
+        <v>3.2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45853.39681537616</v>
+        <v>45853.39681538194</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>19/07 15:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>40</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,187 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45853.39681537616</v>
+        <v>45853.39681538194</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 2.51er set1er participant | Tomas Barr</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tomas Barrios-Vera – Mariano NavoneATP 250 Bastad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 2.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15/07 12:50</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>26,1%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+9,64%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45853.43432757457</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | San Antoni</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo – Once CaldasCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>17/07 00:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+6,43%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45853.43432757457</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | S.Cirstea </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>S.Cirstea – M.BuzarnescuWTA - Iasi</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>15/07 15:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>77,8%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+1,14%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45853.43432757457</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Brann – Re</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brann – Red Bull SalzbourgEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23/07 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>26,9%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+0,95%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45853.43432757457</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>15/07 12:50</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F40" t="n">
+        <v>4.2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45853.43432757457</v>
+        <v>45853.43432756944</v>
       </c>
     </row>
     <row r="41">
@@ -2184,10 +2182,8 @@
           <t>17/07 00:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>45</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2200,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45853.43432757457</v>
+        <v>45853.43432756944</v>
       </c>
     </row>
     <row r="42">
@@ -2229,10 +2225,8 @@
           <t>15/07 15:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="F42" t="n">
+        <v>1.3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2245,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45853.43432757457</v>
+        <v>45853.43432756944</v>
       </c>
     </row>
     <row r="43">
@@ -2274,10 +2268,8 @@
           <t>23/07 17:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="F43" t="n">
+        <v>3.75</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2290,7 +2282,142 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45853.43432757457</v>
+        <v>45853.43432756944</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | HJK Helsin</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HJK Helsinki – AC OuluVeikkausliiga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20/07 15:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+25,3%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45853.4727255387</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Bahia Salv</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Bahia Salvador BA – America de CaliInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16/07 00:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45853.4727255387</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Pas de buts | Nõmme Kalj</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Nõmme Kalju – Tallinna KalevEstonie - Estonie Meistriliiga</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>20/07 14:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+1,38%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45853.4727255387</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>20/07 15:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>60</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45853.4727255387</v>
+        <v>45853.47272554398</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2.75</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45853.4727255387</v>
+        <v>45853.47272554398</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>20/07 14:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>40</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,97 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45853.4727255387</v>
+        <v>45853.47272554398</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 5.51er set1er participant | Ekaterina </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova – Eva VedderWTA 250 Hambourg</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>16/07 08:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>16,2%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+3,37%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45853.53433726608</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 3.5 - tir cadré2e équipe | Bahia Salv</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bahia Salvador BA – America de CaliInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>16/07 00:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>41,2%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+3,04%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45853.53433726608</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -2440,10 +2440,8 @@
           <t>16/07 08:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>6.40</t>
-        </is>
+      <c r="F47" t="n">
+        <v>6.4</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45853.53433726608</v>
+        <v>45853.53433726852</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45853.53433726608</v>
+        <v>45853.53433726852</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,6 +2500,51 @@
         <v>45853.53433726852</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Adam Walto</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Adam Walton – Rodrigo Pacheco MendezATP - Los Cabos</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>16/07 02:10</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>76,3%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+10,6%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45853.59897056227</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>16/07 02:10</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="F49" t="n">
+        <v>1.45</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,142 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45853.59897056227</v>
+        <v>45853.59897056713</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 2.5 - break2e participant | Arthur Caz</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Arthur Cazaux – Tomas Martin EtcheverryATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 2.5 - break2e participant</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>17/07 08:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>59,2%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+6,60%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45853.64175623084</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Philadelph</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Philadelphia Union – CF MontréalMLS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>16/07 23:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+1,21%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45853.64175623084</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | X - aces | M.Barrios </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>M.Barrios Vera – M.NavoneATP - Bastad H</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>15/07 15:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+1,12%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45853.64175623084</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>17/07 08:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F50" t="n">
+        <v>1.8</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45853.64175623084</v>
+        <v>45853.64175622685</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>16/07 23:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>45</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45853.64175623084</v>
+        <v>45853.64175622685</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>15/07 15:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,142 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45853.64175623084</v>
+        <v>45853.64175622685</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | D.Altmaier</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>D.Altmaier – M.KruegerATP - Los Cabos</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>16/07 01:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>89,1%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+11,4%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45853.68771727195</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FK Shkendi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FK Shkendija – The New SaintsLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>15/07 18:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+8,29%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45853.68771727195</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 3.5 - break2e participant | Patrick Za</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Patrick Zahraj – Roman Andres BurruchagaATP - Gstaad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - break2e participant</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>16/07 09:40</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+2,66%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45853.68771727195</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>16/07 01:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
+      <c r="F53" t="n">
+        <v>1.25</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45853.68771727195</v>
+        <v>45853.68771726852</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>15/07 18:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>45</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45853.68771727195</v>
+        <v>45853.68771726852</v>
       </c>
     </row>
     <row r="55">
@@ -2788,10 +2784,8 @@
           <t>16/07 09:40</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.25</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2804,7 +2798,52 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45853.68771727195</v>
+        <v>45853.68771726852</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Levadia Ta</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Levadia Tallinn – Harju JK LaagriEstonie. Estonie - Premier League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19/07 16:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+4,55%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45853.72325462967</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>19/07 16:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>15</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,52 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45853.72325462967</v>
+        <v>45853.72325462963</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Portland T</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Portland Timbers – Real Salt LakeÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>17/07 02:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+1,05%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45853.77433047672</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -2870,10 +2870,8 @@
           <t>17/07 02:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F57" t="n">
+        <v>2.3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45853.77433047672</v>
+        <v>45853.77433047454</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,51 @@
         <v>45853.77433047454</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC KTP – F</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FC KTP – FC Inter TurkuVeikkausliiga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>18/07 15:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+4,44%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45853.85177272857</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>18/07 15:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>45</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,52 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45853.85177272857</v>
+        <v>45853.85177273148</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Santos – F</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Santos – FlamengoSérie A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>16/07 23:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+9,64%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45853.89065690637</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>16/07 23:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>50</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,97 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45853.89065690637</v>
+        <v>45853.89065690972</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Sarmien</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CA Sarmiento – Atletico LanusLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>25/07 22:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+5,90%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45853.93284032581</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | Independie</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Independiente Del Valle – Vasco de GamaInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>16/07 00:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>33,4%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+3,60%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45853.93284032581</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-15.xlsx
+++ b/data/valuebets_database_2025-07-15.xlsx
@@ -2999,10 +2999,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>40</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45853.93284032581</v>
+        <v>45853.93284032407</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>16/07 00:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F61" t="n">
+        <v>3.1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45853.93284032581</v>
+        <v>45853.93284032407</v>
       </c>
     </row>
   </sheetData>
